--- a/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
+++ b/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD DETAIL of STYLE UNION</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 18/05/2026]</t>
+    <t xml:space="preserve">[As on date 23/05/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">DocNo</t>

--- a/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
+++ b/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
@@ -6,21 +6,21 @@
     <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="RD_DETAIL_of_STYLE_UNION" sheetId="1" r:id="rId3"/>
+    <sheet name="RD_DETAIL" sheetId="1" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
   <si>
     <t xml:space="preserve">RD REPORTS</t>
   </si>
   <si>
-    <t xml:space="preserve">RD DETAIL of STYLE UNION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[As on date 23/05/2026]</t>
+    <t xml:space="preserve">RD DETAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[As on date 27/05/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">DocNo</t>
@@ -71,6 +71,45 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">21-05-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales - Computers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">071-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STD RATE COGS ITEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales NewReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYDERABAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Returns VAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor New Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STD RATE COGS ACC INV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchases Voucher VAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor B</t>
+  </si>
+  <si>
     <t xml:space="preserve">25-05-26</t>
   </si>
   <si>
@@ -99,9 +138,6 @@
   </si>
   <si>
     <t xml:space="preserve">AMERICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDERABAD</t>
   </si>
   <si>
     <t xml:space="preserve">STYLE UNION</t>
@@ -494,77 +530,249 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="s">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="9">
+        <v>-2</v>
+      </c>
+      <c r="H7" s="9">
+        <v>10</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="K7"/>
+      <c r="L7" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="M7"/>
+      <c r="N7" s="9">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9">
+        <v>5</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="K8"/>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8"/>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="22" t="s">
+      <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9">
+        <v>5</v>
+      </c>
+      <c r="I9" s="9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="K9"/>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9"/>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9">
+        <v>5</v>
+      </c>
+      <c r="I10" s="9">
+        <v>5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10"/>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8" s="10">
-        <v>100</v>
-      </c>
-      <c r="H8"/>
-      <c r="I8" s="10">
-        <v>5100</v>
-      </c>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8" s="10">
+      <c r="C11" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12" s="10">
+        <v>101</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12" s="10">
+        <v>5110</v>
+      </c>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12" s="10">
         <v>0</v>
       </c>
-      <c r="O8" s="10">
-        <v>5100</v>
+      <c r="O12" s="10">
+        <v>5095</v>
       </c>
     </row>
   </sheetData>

--- a/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
+++ b/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD DETAIL of STYLE UNION</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 04/06/2026]</t>
+    <t xml:space="preserve">[As on date 05/06/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">DocNo</t>

--- a/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
+++ b/autoIt/ExportFiles/RDDetailExcelEntryNew.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD DETAIL of STYLE UNION</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 05/06/2026]</t>
+    <t xml:space="preserve">[As on date 22/06/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">DocNo</t>
